--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14018,7 +14018,7 @@
         <v>117810144</v>
       </c>
       <c r="B114" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY114"/>
+  <dimension ref="A1:AY118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14132,6 +14132,459 @@
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>120120595</v>
+      </c>
+      <c r="B115" t="n">
+        <v>90124</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>937</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Vit vedfingersvamp</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Lentaria epichnoa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Ekebylund, Upl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>649753</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6648844</v>
+      </c>
+      <c r="S115" t="n">
+        <v>50</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Erik Berg</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>120121934</v>
+      </c>
+      <c r="B116" t="n">
+        <v>91005</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Ekeby, Upl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>649910</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6649024</v>
+      </c>
+      <c r="S116" t="n">
+        <v>25</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre barkborreträd</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Erik Berg</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>120120550</v>
+      </c>
+      <c r="B117" t="n">
+        <v>91317</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>366</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Ekebylund, Upl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>649753</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6648844</v>
+      </c>
+      <c r="S117" t="n">
+        <v>50</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Erik Berg</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>120120686</v>
+      </c>
+      <c r="B118" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Ekebylund, Upl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>649834</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6648750</v>
+      </c>
+      <c r="S118" t="n">
+        <v>25</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Erik Berg</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14134,10 +14134,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120120595</v>
+        <v>120120686</v>
       </c>
       <c r="B115" t="n">
-        <v>90124</v>
+        <v>90562</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14150,21 +14150,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>937</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14174,13 +14174,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>649753</v>
+        <v>649834</v>
       </c>
       <c r="R115" t="n">
-        <v>6648844</v>
+        <v>6648750</v>
       </c>
       <c r="S115" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14475,10 +14475,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120120686</v>
+        <v>120120595</v>
       </c>
       <c r="B118" t="n">
-        <v>90562</v>
+        <v>90124</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14491,21 +14491,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>937</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14515,13 +14515,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>649834</v>
+        <v>649753</v>
       </c>
       <c r="R118" t="n">
-        <v>6648750</v>
+        <v>6648844</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14134,10 +14134,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120120686</v>
+        <v>120120550</v>
       </c>
       <c r="B115" t="n">
-        <v>90562</v>
+        <v>91317</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14150,21 +14150,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>366</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14174,13 +14174,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>649834</v>
+        <v>649753</v>
       </c>
       <c r="R115" t="n">
-        <v>6648750</v>
+        <v>6648844</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14246,10 +14246,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120121934</v>
+        <v>120120686</v>
       </c>
       <c r="B116" t="n">
-        <v>91005</v>
+        <v>90562</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14258,38 +14258,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Ekeby, Upl</t>
+          <t>Ekebylund, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>649910</v>
+        <v>649834</v>
       </c>
       <c r="R116" t="n">
-        <v>6649024</v>
+        <v>6648750</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14321,7 +14321,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14331,12 +14331,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre barkborreträd</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14363,10 +14358,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120120550</v>
+        <v>120121934</v>
       </c>
       <c r="B117" t="n">
-        <v>91317</v>
+        <v>91005</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14375,41 +14370,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>366</v>
+        <v>1209</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ekebylund, Upl</t>
+          <t>Ekeby, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>649753</v>
+        <v>649910</v>
       </c>
       <c r="R117" t="n">
-        <v>6648844</v>
+        <v>6649024</v>
       </c>
       <c r="S117" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14438,7 +14433,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14448,7 +14443,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Äldre barkborreträd</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY118"/>
+  <dimension ref="A1:AY119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14585,6 +14585,123 @@
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>120281713</v>
+      </c>
+      <c r="B119" t="n">
+        <v>4772</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Norrbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>650396</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6648464</v>
+      </c>
+      <c r="S119" t="n">
+        <v>15</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Erik Berg</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Erik Berg</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14137,7 +14137,7 @@
         <v>120120550</v>
       </c>
       <c r="B115" t="n">
-        <v>91317</v>
+        <v>91335</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>120120686</v>
       </c>
       <c r="B116" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>120121934</v>
       </c>
       <c r="B117" t="n">
-        <v>91005</v>
+        <v>91023</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>120120595</v>
       </c>
       <c r="B118" t="n">
-        <v>90124</v>
+        <v>90141</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14134,10 +14134,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120120550</v>
+        <v>120120686</v>
       </c>
       <c r="B115" t="n">
-        <v>91335</v>
+        <v>90580</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14150,21 +14150,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>366</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14174,13 +14174,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>649753</v>
+        <v>649834</v>
       </c>
       <c r="R115" t="n">
-        <v>6648844</v>
+        <v>6648750</v>
       </c>
       <c r="S115" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14246,10 +14246,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120120686</v>
+        <v>120121934</v>
       </c>
       <c r="B116" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14258,38 +14258,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Ekebylund, Upl</t>
+          <t>Ekeby, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>649834</v>
+        <v>649910</v>
       </c>
       <c r="R116" t="n">
-        <v>6648750</v>
+        <v>6649024</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -14321,7 +14321,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14331,7 +14331,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre barkborreträd</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14358,10 +14363,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120121934</v>
+        <v>120120595</v>
       </c>
       <c r="B117" t="n">
-        <v>91023</v>
+        <v>90141</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14370,41 +14375,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1209</v>
+        <v>937</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ekeby, Upl</t>
+          <t>Ekebylund, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>649910</v>
+        <v>649753</v>
       </c>
       <c r="R117" t="n">
-        <v>6649024</v>
+        <v>6648844</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14433,7 +14438,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14443,12 +14448,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre barkborreträd</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14475,10 +14475,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120120595</v>
+        <v>120120550</v>
       </c>
       <c r="B118" t="n">
-        <v>90141</v>
+        <v>91335</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14491,21 +14491,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>937</v>
+        <v>366</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14550,7 +14550,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14363,10 +14363,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120120595</v>
+        <v>120120550</v>
       </c>
       <c r="B117" t="n">
-        <v>90141</v>
+        <v>91335</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14379,21 +14379,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>937</v>
+        <v>366</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14475,10 +14475,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120120550</v>
+        <v>120120595</v>
       </c>
       <c r="B118" t="n">
-        <v>91335</v>
+        <v>90141</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14491,21 +14491,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>366</v>
+        <v>937</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14550,7 +14550,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14246,10 +14246,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120121934</v>
+        <v>120120550</v>
       </c>
       <c r="B116" t="n">
-        <v>91023</v>
+        <v>91335</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14258,41 +14258,41 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1209</v>
+        <v>366</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Ekeby, Upl</t>
+          <t>Ekebylund, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>649910</v>
+        <v>649753</v>
       </c>
       <c r="R116" t="n">
-        <v>6649024</v>
+        <v>6648844</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14331,12 +14331,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre barkborreträd</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14363,10 +14358,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120120550</v>
+        <v>120121934</v>
       </c>
       <c r="B117" t="n">
-        <v>91335</v>
+        <v>91023</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14375,41 +14370,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>366</v>
+        <v>1209</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ekebylund, Upl</t>
+          <t>Ekeby, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>649753</v>
+        <v>649910</v>
       </c>
       <c r="R117" t="n">
-        <v>6648844</v>
+        <v>6649024</v>
       </c>
       <c r="S117" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14438,7 +14433,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14448,7 +14443,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Äldre barkborreträd</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14134,10 +14134,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120120686</v>
+        <v>120121934</v>
       </c>
       <c r="B115" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14146,38 +14146,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Ekebylund, Upl</t>
+          <t>Ekeby, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>649834</v>
+        <v>649910</v>
       </c>
       <c r="R115" t="n">
-        <v>6648750</v>
+        <v>6649024</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14219,7 +14219,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Äldre barkborreträd</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14246,10 +14251,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120120550</v>
+        <v>120120686</v>
       </c>
       <c r="B116" t="n">
-        <v>91335</v>
+        <v>90580</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14262,21 +14267,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>366</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14286,13 +14291,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>649753</v>
+        <v>649834</v>
       </c>
       <c r="R116" t="n">
-        <v>6648844</v>
+        <v>6648750</v>
       </c>
       <c r="S116" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14321,7 +14326,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14331,7 +14336,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14358,10 +14363,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120121934</v>
+        <v>120120550</v>
       </c>
       <c r="B117" t="n">
-        <v>91023</v>
+        <v>91335</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14370,41 +14375,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1209</v>
+        <v>366</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ekeby, Upl</t>
+          <t>Ekebylund, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>649910</v>
+        <v>649753</v>
       </c>
       <c r="R117" t="n">
-        <v>6649024</v>
+        <v>6648844</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14433,7 +14438,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14443,12 +14448,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre barkborreträd</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14134,10 +14134,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120121934</v>
+        <v>120120595</v>
       </c>
       <c r="B115" t="n">
-        <v>91023</v>
+        <v>90141</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14146,41 +14146,41 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1209</v>
+        <v>937</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Ekeby, Upl</t>
+          <t>Ekebylund, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>649910</v>
+        <v>649753</v>
       </c>
       <c r="R115" t="n">
-        <v>6649024</v>
+        <v>6648844</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14219,12 +14219,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Äldre barkborreträd</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14363,10 +14358,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120120550</v>
+        <v>120121934</v>
       </c>
       <c r="B117" t="n">
-        <v>91335</v>
+        <v>91023</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14375,41 +14370,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>366</v>
+        <v>1209</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ekebylund, Upl</t>
+          <t>Ekeby, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>649753</v>
+        <v>649910</v>
       </c>
       <c r="R117" t="n">
-        <v>6648844</v>
+        <v>6649024</v>
       </c>
       <c r="S117" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14438,7 +14433,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14448,7 +14443,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Äldre barkborreträd</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14475,10 +14475,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120120595</v>
+        <v>120120550</v>
       </c>
       <c r="B118" t="n">
-        <v>90141</v>
+        <v>91335</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14491,21 +14491,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>937</v>
+        <v>366</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14550,7 +14550,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14134,10 +14134,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120120595</v>
+        <v>120120550</v>
       </c>
       <c r="B115" t="n">
-        <v>90141</v>
+        <v>91335</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14150,21 +14150,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>937</v>
+        <v>366</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14246,10 +14246,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120120686</v>
+        <v>120120595</v>
       </c>
       <c r="B116" t="n">
-        <v>90580</v>
+        <v>90141</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14262,21 +14262,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>937</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14286,13 +14286,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>649834</v>
+        <v>649753</v>
       </c>
       <c r="R116" t="n">
-        <v>6648750</v>
+        <v>6648844</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14475,10 +14475,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120120550</v>
+        <v>120120686</v>
       </c>
       <c r="B118" t="n">
-        <v>91335</v>
+        <v>90580</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14491,21 +14491,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>366</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14515,13 +14515,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>649753</v>
+        <v>649834</v>
       </c>
       <c r="R118" t="n">
-        <v>6648844</v>
+        <v>6648750</v>
       </c>
       <c r="S118" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14134,10 +14134,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120120550</v>
+        <v>120121934</v>
       </c>
       <c r="B115" t="n">
-        <v>91335</v>
+        <v>91023</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14146,41 +14146,41 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>366</v>
+        <v>1209</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Ekebylund, Upl</t>
+          <t>Ekeby, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>649753</v>
+        <v>649910</v>
       </c>
       <c r="R115" t="n">
-        <v>6648844</v>
+        <v>6649024</v>
       </c>
       <c r="S115" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14219,7 +14219,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Äldre barkborreträd</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14246,10 +14251,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120120595</v>
+        <v>120120686</v>
       </c>
       <c r="B116" t="n">
-        <v>90141</v>
+        <v>90580</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14262,21 +14267,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>937</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14286,13 +14291,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>649753</v>
+        <v>649834</v>
       </c>
       <c r="R116" t="n">
-        <v>6648844</v>
+        <v>6648750</v>
       </c>
       <c r="S116" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14358,10 +14363,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120121934</v>
+        <v>120120595</v>
       </c>
       <c r="B117" t="n">
-        <v>91023</v>
+        <v>90141</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14370,41 +14375,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1209</v>
+        <v>937</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ekeby, Upl</t>
+          <t>Ekebylund, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>649910</v>
+        <v>649753</v>
       </c>
       <c r="R117" t="n">
-        <v>6649024</v>
+        <v>6648844</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14433,7 +14438,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14443,12 +14448,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre barkborreträd</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14475,10 +14475,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120120686</v>
+        <v>120120550</v>
       </c>
       <c r="B118" t="n">
-        <v>90580</v>
+        <v>91335</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14491,21 +14491,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>366</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14515,13 +14515,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>649834</v>
+        <v>649753</v>
       </c>
       <c r="R118" t="n">
-        <v>6648750</v>
+        <v>6648844</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY119"/>
+  <dimension ref="A1:AY120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14702,6 +14702,127 @@
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>123242068</v>
+      </c>
+      <c r="B120" t="n">
+        <v>91397</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Storvreta, SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>649926</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6649068</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14707,7 +14707,7 @@
         <v>123242068</v>
       </c>
       <c r="B120" t="n">
-        <v>91397</v>
+        <v>91400</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14707,7 +14707,7 @@
         <v>123242068</v>
       </c>
       <c r="B120" t="n">
-        <v>91400</v>
+        <v>91402</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14707,7 +14707,7 @@
         <v>123242068</v>
       </c>
       <c r="B120" t="n">
-        <v>91402</v>
+        <v>91408</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14707,7 +14707,7 @@
         <v>123242068</v>
       </c>
       <c r="B120" t="n">
-        <v>91411</v>
+        <v>91428</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -14707,7 +14707,7 @@
         <v>123242068</v>
       </c>
       <c r="B120" t="n">
-        <v>91428</v>
+        <v>91433</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>

--- a/artfynd/A 31276-2020 artfynd.xlsx
+++ b/artfynd/A 31276-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY120"/>
+  <dimension ref="A1:AY119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6721,7 +6721,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>76621800</v>
+        <v>76883834</v>
       </c>
       <c r="B53" t="n">
         <v>81972</v>
@@ -6759,26 +6759,20 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Himmelsvägen, Storvreta, Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649925.2046247883</v>
+        <v>649921.6192182691</v>
       </c>
       <c r="R53" t="n">
-        <v>6649075.059463935</v>
+        <v>6649064.382571468</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6802,27 +6796,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2019-03-27</t>
+          <t>2019-04-07</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2019-03-27</t>
+          <t>2019-04-07</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6831,31 +6820,25 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>äldre granskog</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Bengt Neiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Håkan Lernefalk, Patrick Fritzson</t>
+          <t>Bengt Neiss</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>76883834</v>
+        <v>81674872</v>
       </c>
       <c r="B54" t="n">
         <v>81972</v>
@@ -6890,23 +6873,25 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>Storvreta, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>649921.6192182691</v>
+        <v>649933.6962494765</v>
       </c>
       <c r="R54" t="n">
-        <v>6649064.382571468</v>
+        <v>6649063.869745764</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6930,22 +6915,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2019-04-07</t>
+          <t>2020-01-08</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2019-04-07</t>
+          <t>2020-01-08</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Känd lokal</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6954,25 +6944,26 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bengt Neiss</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Neiss</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>81674872</v>
+        <v>81674864</v>
       </c>
       <c r="B55" t="n">
         <v>81972</v>
@@ -7019,10 +7010,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>649933.6962494765</v>
+        <v>649948.6532497486</v>
       </c>
       <c r="R55" t="n">
-        <v>6649063.869745764</v>
+        <v>6649041.909500772</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7069,7 +7060,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Känd lokal</t>
+          <t>Känd lokal.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7097,7 +7088,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>81674864</v>
+        <v>16990265</v>
       </c>
       <c r="B56" t="n">
         <v>81972</v>
@@ -7135,22 +7126,24 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storvreta, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>649948.6532497486</v>
+        <v>649958.7512043342</v>
       </c>
       <c r="R56" t="n">
-        <v>6649041.909500772</v>
+        <v>6649028.277430258</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7174,7 +7167,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2020-01-08</t>
+          <t>2014-03-28</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -7184,7 +7177,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2020-01-08</t>
+          <t>2014-03-28</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -7194,7 +7187,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Känd lokal.</t>
+          <t>2 ex. i barrförna mellan stora stenblock, äldre granskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7203,26 +7196,30 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Blockrik, äldre granskog.</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>16990265</v>
+        <v>16990266</v>
       </c>
       <c r="B57" t="n">
         <v>81972</v>
@@ -7257,7 +7254,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7271,10 +7268,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>649958.7512043342</v>
+        <v>649909.617029862</v>
       </c>
       <c r="R57" t="n">
-        <v>6649028.277430258</v>
+        <v>6649075.429845632</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7321,7 +7318,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>2 ex. i barrförna mellan stora stenblock, äldre granskog.</t>
+          <t>14 ex. i barrförna och i vegetation av vägg- och husmossa samt blåbärsris, i blockrik äldre granskog. Upptäckt av Robert Weimer, Storvreta.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7353,10 +7350,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>16990266</v>
+        <v>82551986</v>
       </c>
       <c r="B58" t="n">
-        <v>81972</v>
+        <v>56540</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7365,50 +7362,49 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1445</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storvreta, Upl</t>
+          <t>NV. Slöjmolnsvägen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>649909.617029862</v>
+        <v>649949.9336180199</v>
       </c>
       <c r="R58" t="n">
-        <v>6649075.429845632</v>
+        <v>6649010.366950603</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7432,27 +7428,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2014-03-28</t>
+          <t>2020-03-02</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2014-03-28</t>
+          <t>2020-03-02</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>14 ex. i barrförna och i vegetation av vägg- och husmossa samt blåbärsris, i blockrik äldre granskog. Upptäckt av Robert Weimer, Storvreta.</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7463,31 +7454,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Blockrik, äldre granskog.</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Håkan Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Håkan Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>82551986</v>
+        <v>87987105</v>
       </c>
       <c r="B59" t="n">
-        <v>56540</v>
+        <v>57587</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7496,49 +7482,49 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>100141</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>NV. Slöjmolnsvägen, Upl</t>
+          <t>kärr, Storvreta, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>649949.9336180199</v>
+        <v>650176.5398906262</v>
       </c>
       <c r="R59" t="n">
-        <v>6649010.366950603</v>
+        <v>6648539.601830478</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7562,22 +7548,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2020-03-02</t>
+          <t>2000-06-01</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2020-03-02</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>UT och min son har från det vi flyttade till Storvreta sett Större vattensalamander och Mindre vattensalamander i kärret vid Himmelsvägen/Storvreta.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7588,23 +7579,28 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Kärr med barrträd</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Andersson</t>
+          <t>Elisabeth Fleischer</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Andersson</t>
+          <t>Elisabeth Fleischer</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>87987105</v>
+        <v>88027608</v>
       </c>
       <c r="B60" t="n">
         <v>57587</v>
@@ -7637,10 +7633,27 @@
           <t>(Laurenti, 1768)</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7648,17 +7661,17 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>kärr, Storvreta, Upl</t>
+          <t>Kärret Himmelsvägen ,Storvreta, Storvreta, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>650176.5398906262</v>
+        <v>649979.5920501237</v>
       </c>
       <c r="R60" t="n">
-        <v>6648539.601830478</v>
+        <v>6648539.626991335</v>
       </c>
       <c r="S60" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7682,7 +7695,7 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2000-06-01</t>
+          <t>2000-06-10</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -7692,7 +7705,7 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -7702,7 +7715,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>UT och min son har från det vi flyttade till Storvreta sett Större vattensalamander och Mindre vattensalamander i kärret vid Himmelsvägen/Storvreta.</t>
+          <t>Förekommer varje år i kärret, intill Himmelsvägen i Storvreta</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7711,33 +7724,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Kärr med barrträd</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elisabeth Fleischer</t>
+          <t>Christoffer Fruh</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elisabeth Fleischer</t>
+          <t>Christoffer Fruh</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>88027608</v>
+        <v>88025862</v>
       </c>
       <c r="B61" t="n">
-        <v>57587</v>
+        <v>90008</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7750,62 +7759,44 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100141</v>
+        <v>6031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kärret Himmelsvägen ,Storvreta, Storvreta, Upl</t>
+          <t>Blomkålssvamp, Storvreta, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>649979.5920501237</v>
+        <v>650303.434126305</v>
       </c>
       <c r="R61" t="n">
-        <v>6648539.626991335</v>
+        <v>6648458.49077496</v>
       </c>
       <c r="S61" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7829,7 +7820,7 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2000-06-10</t>
+          <t>2020-09-13</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -7839,7 +7830,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-09-13</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -7849,7 +7840,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Förekommer varje år i kärret, intill Himmelsvägen i Storvreta</t>
+          <t>Undertecknad har under flera år träffat på Blomkålssvamp/ Sparassis crispa i området!</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7865,22 +7856,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Christoffer Fruh</t>
+          <t>Elisabeth Fleischer</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Christoffer Fruh</t>
+          <t>Elisabeth Fleischer</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>88025862</v>
+        <v>88027752</v>
       </c>
       <c r="B62" t="n">
-        <v>90008</v>
+        <v>57585</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7893,44 +7884,54 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6031</v>
+        <v>208242</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Blomkålssvamp, Storvreta, Upl</t>
+          <t>Kärret Himmelsvägen ,Storvreta, Storvreta, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>650303.434126305</v>
+        <v>649979.5920501237</v>
       </c>
       <c r="R62" t="n">
-        <v>6648458.49077496</v>
+        <v>6648539.626991335</v>
       </c>
       <c r="S62" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7954,7 +7955,7 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2020-09-13</t>
+          <t>2000-05-31</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -7964,7 +7965,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2020-09-13</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
@@ -7974,7 +7975,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Undertecknad har under flera år träffat på Blomkålssvamp/ Sparassis crispa i området!</t>
+          <t>Flitigt förekommande i kärret vid Himmelsvägen/ Storvreta</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7990,22 +7991,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Elisabeth Fleischer</t>
+          <t>Christoffer Fruh</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elisabeth Fleischer</t>
+          <t>Christoffer Fruh</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>88027752</v>
+        <v>88159445</v>
       </c>
       <c r="B63" t="n">
-        <v>57585</v>
+        <v>88896</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8014,58 +8015,44 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>208242</v>
+        <v>720</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kärret Himmelsvägen ,Storvreta, Storvreta, Upl</t>
+          <t>Fulleröskogen 2, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>649979.5920501237</v>
+        <v>650017.9102202069</v>
       </c>
       <c r="R63" t="n">
-        <v>6648539.626991335</v>
+        <v>6648771.394573689</v>
       </c>
       <c r="S63" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8089,7 +8076,7 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2000-05-31</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -8099,7 +8086,7 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
@@ -8109,7 +8096,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Flitigt förekommande i kärret vid Himmelsvägen/ Storvreta</t>
+          <t>Häxring ca 2m</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8125,19 +8112,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Christoffer Fruh</t>
+          <t>David  Englund</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Christoffer Fruh</t>
+          <t>David  Englund</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>88159445</v>
+        <v>88159476</v>
       </c>
       <c r="B64" t="n">
         <v>88896</v>
@@ -8176,14 +8163,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fulleröskogen 2, Upl</t>
+          <t>Fulleröskogen 2b, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>650017.9102202069</v>
+        <v>650007.0996209418</v>
       </c>
       <c r="R64" t="n">
-        <v>6648771.394573689</v>
+        <v>6648765.438713368</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8226,11 +8213,6 @@
       <c r="AB64" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Häxring ca 2m</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8258,7 +8240,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>88159476</v>
+        <v>88159247</v>
       </c>
       <c r="B65" t="n">
         <v>88896</v>
@@ -8291,20 +8273,28 @@
           <t>(Pers.) Gray</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fulleröskogen 2b, Upl</t>
+          <t>Fulleröskogen 1, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>650007.0996209418</v>
+        <v>649981.6527977665</v>
       </c>
       <c r="R65" t="n">
-        <v>6648765.438713368</v>
+        <v>6648550.745085942</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8374,10 +8364,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>88159247</v>
+        <v>88416025</v>
       </c>
       <c r="B66" t="n">
-        <v>88896</v>
+        <v>89392</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8386,52 +8376,44 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>720</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fulleröskogen 1, Upl</t>
+          <t>kalkbarrskog väster om himmelsvägen, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>649981.6527977665</v>
+        <v>649978.6800961911</v>
       </c>
       <c r="R66" t="n">
-        <v>6648550.745085942</v>
+        <v>6648747.734162644</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8455,7 +8437,7 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
@@ -8465,12 +8447,17 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>rikligt på granlåga</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8486,22 +8473,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>David  Englund</t>
+          <t>Gry Benediktson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>David  Englund</t>
+          <t>Gry Benediktson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>88416025</v>
+        <v>88415103</v>
       </c>
       <c r="B67" t="n">
-        <v>89392</v>
+        <v>90339</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8510,25 +8497,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>4787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8541,13 +8528,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649978.6800961911</v>
+        <v>650102.405275509</v>
       </c>
       <c r="R67" t="n">
-        <v>6648747.734162644</v>
+        <v>6648608.312863322</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8591,7 +8578,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>rikligt på granlåga</t>
+          <t>ett par exemplar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8619,10 +8606,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>88415103</v>
+        <v>88414937</v>
       </c>
       <c r="B68" t="n">
-        <v>90339</v>
+        <v>90008</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8635,21 +8622,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4787</v>
+        <v>6031</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8662,10 +8649,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>650102.405275509</v>
+        <v>649998.4162223396</v>
       </c>
       <c r="R68" t="n">
-        <v>6648608.312863322</v>
+        <v>6648645.2170744</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8708,11 +8695,6 @@
       <c r="AB68" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>ett par exemplar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8740,10 +8722,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>88414937</v>
+        <v>88538479</v>
       </c>
       <c r="B69" t="n">
-        <v>90008</v>
+        <v>90665</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8756,24 +8738,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6031</v>
+        <v>4366</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
@@ -8783,13 +8769,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>649998.4162223396</v>
+        <v>649856.8486212983</v>
       </c>
       <c r="R69" t="n">
-        <v>6648645.2170744</v>
+        <v>6649051.223038451</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8813,7 +8799,7 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
+          <t>2020-10-12</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
@@ -8823,7 +8809,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
+          <t>2020-10-12</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -8856,10 +8842,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>88538479</v>
+        <v>88538630</v>
       </c>
       <c r="B70" t="n">
-        <v>90665</v>
+        <v>90674</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8872,28 +8858,24 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -8903,10 +8885,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>649856.8486212983</v>
+        <v>649990.7966992285</v>
       </c>
       <c r="R70" t="n">
-        <v>6649051.223038451</v>
+        <v>6648560.646001516</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8949,6 +8931,11 @@
       <c r="AB70" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Inom 20 meters radie finns flera ringar. arten är vanlig i alla grandominerade svackor av skogen.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8976,10 +8963,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>88538630</v>
+        <v>88538496</v>
       </c>
       <c r="B71" t="n">
-        <v>90674</v>
+        <v>90665</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8992,24 +8979,28 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
@@ -9019,10 +9010,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>649990.7966992285</v>
+        <v>649868.3806176679</v>
       </c>
       <c r="R71" t="n">
-        <v>6648560.646001516</v>
+        <v>6648977.468746475</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9065,11 +9056,6 @@
       <c r="AB71" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Inom 20 meters radie finns flera ringar. arten är vanlig i alla grandominerade svackor av skogen.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9097,10 +9083,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>88538496</v>
+        <v>91487884</v>
       </c>
       <c r="B72" t="n">
-        <v>90665</v>
+        <v>89392</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9109,32 +9095,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4366</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
@@ -9144,13 +9126,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>649868.3806176679</v>
+        <v>649998.4162223396</v>
       </c>
       <c r="R72" t="n">
-        <v>6648977.468746475</v>
+        <v>6648645.2170744</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9174,7 +9156,7 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2020-10-12</t>
+          <t>2020-11-29</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
@@ -9184,7 +9166,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2020-10-12</t>
+          <t>2020-11-29</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
@@ -9217,10 +9199,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>91487884</v>
+        <v>92107012</v>
       </c>
       <c r="B73" t="n">
-        <v>89392</v>
+        <v>98520</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9229,41 +9211,50 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>kalkbarrskog väster om himmelsvägen, Upl</t>
+          <t>Cykelvägen, Slöjmolnsväegn, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>649998.4162223396</v>
+        <v>649991.8176454952</v>
       </c>
       <c r="R73" t="n">
-        <v>6648645.2170744</v>
+        <v>6649018.085362031</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9290,22 +9281,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2020-11-29</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2020-11-29</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9314,29 +9305,28 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Gry Benediktson</t>
+          <t>Bengt Neiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Gry Benediktson</t>
+          <t>Bengt Neiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>92107012</v>
+        <v>96153766</v>
       </c>
       <c r="B74" t="n">
-        <v>98520</v>
+        <v>85172</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9345,53 +9335,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Cykelvägen, Slöjmolnsväegn, Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>649991.8176454952</v>
+        <v>649874.0641054707</v>
       </c>
       <c r="R74" t="n">
-        <v>6649018.085362031</v>
+        <v>6649085.020045049</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9415,22 +9394,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9445,22 +9424,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bengt Neiss</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bengt Neiss</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>96153766</v>
+        <v>96187232</v>
       </c>
       <c r="B75" t="n">
-        <v>85172</v>
+        <v>90674</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9469,42 +9448,44 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>442</v>
+        <v>5964</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>kalkbarrskog väster om himmelsvägen, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>649874.0641054707</v>
+        <v>650168.6425140236</v>
       </c>
       <c r="R75" t="n">
-        <v>6649085.020045049</v>
+        <v>6648560.848235592</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9528,7 +9509,7 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
@@ -9538,7 +9519,7 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
@@ -9546,34 +9527,40 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>förekommer rikligt i skogsområdet. stora exemplar och stora, täta ringar finns.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Gry Benediktson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Gry Benediktson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>96187232</v>
+        <v>96187044</v>
       </c>
       <c r="B76" t="n">
-        <v>90674</v>
+        <v>88921</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9586,21 +9573,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9613,10 +9600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>650168.6425140236</v>
+        <v>650108.6112923591</v>
       </c>
       <c r="R76" t="n">
-        <v>6648560.848235592</v>
+        <v>6648739.97105081</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9643,7 +9630,7 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
@@ -9653,17 +9640,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>förekommer rikligt i skogsområdet. stora exemplar och stora, täta ringar finns.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9691,10 +9673,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>96187044</v>
+        <v>96187129</v>
       </c>
       <c r="B77" t="n">
-        <v>88921</v>
+        <v>90319</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9707,21 +9689,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5741</v>
+        <v>4769</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9734,10 +9716,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>650108.6112923591</v>
+        <v>650140.5394960955</v>
       </c>
       <c r="R77" t="n">
-        <v>6648739.97105081</v>
+        <v>6648584.784313248</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9764,7 +9746,7 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
@@ -9774,12 +9756,17 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>vanlig i denna granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9807,10 +9794,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>96187129</v>
+        <v>96214327</v>
       </c>
       <c r="B78" t="n">
-        <v>90319</v>
+        <v>85301</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9819,44 +9806,42 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4769</v>
+        <v>3739</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>kalkbarrskog väster om himmelsvägen, Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>650140.5394960955</v>
+        <v>649916.3037831903</v>
       </c>
       <c r="R78" t="n">
-        <v>6648584.784313248</v>
+        <v>6648984.929825474</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9880,7 +9865,7 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
@@ -9890,7 +9875,7 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -9898,40 +9883,34 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>vanlig i denna granskog</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Gry Benediktson</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Gry Benediktson</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>96214327</v>
+        <v>96308849</v>
       </c>
       <c r="B79" t="n">
-        <v>85301</v>
+        <v>88921</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9940,42 +9919,44 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3739</v>
+        <v>5741</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>Barrskog SV Himmelsvägen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>649916.3037831903</v>
+        <v>650196.6441188324</v>
       </c>
       <c r="R79" t="n">
-        <v>6648984.929825474</v>
+        <v>6648539.415906242</v>
       </c>
       <c r="S79" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9999,7 +9980,7 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
@@ -10009,7 +9990,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
@@ -10023,28 +10004,29 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Gry Benediktson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Gry Benediktson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>96308849</v>
+        <v>96746403</v>
       </c>
       <c r="B80" t="n">
-        <v>88921</v>
+        <v>89412</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10053,25 +10035,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5741</v>
+        <v>5442</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10080,14 +10062,14 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Barrskog SV Himmelsvägen, Upl</t>
+          <t>barrblandskog N vintergatsvägen, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>650196.6441188324</v>
+        <v>650057.0445075793</v>
       </c>
       <c r="R80" t="n">
-        <v>6648539.415906242</v>
+        <v>6649366.253520134</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10114,7 +10096,7 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
@@ -10124,7 +10106,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
@@ -10157,10 +10139,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>96746403</v>
+        <v>97742393</v>
       </c>
       <c r="B81" t="n">
-        <v>89412</v>
+        <v>90674</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10169,25 +10151,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5442</v>
+        <v>5964</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10196,17 +10178,17 @@
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>barrblandskog N vintergatsvägen, Upl</t>
+          <t>Storvreta SV, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>650057.0445075793</v>
+        <v>649873.6361577424</v>
       </c>
       <c r="R81" t="n">
-        <v>6649366.253520134</v>
+        <v>6649058.423540089</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10230,7 +10212,7 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
@@ -10240,7 +10222,7 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
@@ -10261,22 +10243,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Gry Benediktson</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Gry Benediktson</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>97742393</v>
+        <v>98639094</v>
       </c>
       <c r="B82" t="n">
-        <v>90674</v>
+        <v>85254</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10289,40 +10271,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5964</v>
+        <v>249228</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Storvreta SV, Upl</t>
+          <t>Sverige, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>649873.6361577424</v>
+        <v>649853.8254448548</v>
       </c>
       <c r="R82" t="n">
-        <v>6649058.423540089</v>
+        <v>6649039.064480114</v>
       </c>
       <c r="S82" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10346,7 +10325,7 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
@@ -10356,7 +10335,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
@@ -10370,29 +10349,28 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>98639094</v>
+        <v>98639067</v>
       </c>
       <c r="B83" t="n">
-        <v>85254</v>
+        <v>85301</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10401,25 +10379,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>249228</v>
+        <v>3739</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10429,10 +10407,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>649853.8254448548</v>
+        <v>649844.3151867579</v>
       </c>
       <c r="R83" t="n">
-        <v>6649039.064480114</v>
+        <v>6649001.066208675</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10501,10 +10479,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>98639067</v>
+        <v>103428243</v>
       </c>
       <c r="B84" t="n">
-        <v>85301</v>
+        <v>90008</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10513,38 +10491,45 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3739</v>
+        <v>6031</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sverige, Upl</t>
+          <t>barrskog V Himmelsvägen, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>649844.3151867579</v>
+        <v>650325.4054360926</v>
       </c>
       <c r="R84" t="n">
-        <v>6649001.066208675</v>
+        <v>6648424.775329884</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10571,7 +10556,7 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
@@ -10581,7 +10566,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
@@ -10589,34 +10574,40 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>vid foten av tall norr om stig.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Gry Benediktson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Gry Benediktson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>103428243</v>
+        <v>85576877</v>
       </c>
       <c r="B85" t="n">
-        <v>90008</v>
+        <v>57587</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10629,21 +10620,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6031</v>
+        <v>100141</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10651,19 +10642,41 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>barrskog V Himmelsvägen, Upl</t>
+          <t>Salamanderkärret, Storvreta, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>650325.4054360926</v>
+        <v>649983.3425768835</v>
       </c>
       <c r="R85" t="n">
-        <v>6648424.775329884</v>
+        <v>6648694.760004896</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10690,27 +10703,27 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>vid foten av tall norr om stig.</t>
+          <t>Fint exemplar, hona, ca. 16 cm lång med svans. Svart och knottrig med orange/gul spräcklig mage.  Salamandrar har observerats i kärret sedan början av 90-talet. Den lilla skogen runt kärret är fin med mycket död ved. Det finns ett mindre kärr norr om fyndplatsen. Det finns ett dräneringsdike i den södra delen av vårmarken som inte lyckats dränera det. Kärren är igenväxta men flera vattenspeglar finns.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10726,22 +10739,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Gry Benediktson</t>
+          <t>Robert Harlin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Gry Benediktson</t>
+          <t>Robert Harlin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>85576877</v>
+        <v>107841893</v>
       </c>
       <c r="B86" t="n">
-        <v>57587</v>
+        <v>89392</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10750,70 +10763,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100141</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>slag-/vattenhåvning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Salamanderkärret, Storvreta, Upl</t>
+          <t>Fullerömyren, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>649983.3425768835</v>
+        <v>650121.3830034449</v>
       </c>
       <c r="R86" t="n">
-        <v>6648694.760004896</v>
+        <v>6648648.205299131</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10837,27 +10822,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Fint exemplar, hona, ca. 16 cm lång med svans. Svart och knottrig med orange/gul spräcklig mage.  Salamandrar har observerats i kärret sedan början av 90-talet. Den lilla skogen runt kärret är fin med mycket död ved. Det finns ett mindre kärr norr om fyndplatsen. Det finns ett dräneringsdike i den södra delen av vårmarken som inte lyckats dränera det. Kärren är igenväxta men flera vattenspeglar finns.</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10866,29 +10846,28 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Robert Harlin</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Robert Harlin</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>107841893</v>
+        <v>107839427</v>
       </c>
       <c r="B87" t="n">
-        <v>89392</v>
+        <v>89940</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10897,39 +10876,39 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>3884</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fullerömyren, Upl</t>
+          <t>Skarpan, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>650121.3830034449</v>
+        <v>649859.3531147883</v>
       </c>
       <c r="R87" t="n">
-        <v>6648648.205299131</v>
+        <v>6648977.102519212</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10961,7 +10940,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10971,7 +10950,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10998,10 +10977,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>107839427</v>
+        <v>107841560</v>
       </c>
       <c r="B88" t="n">
-        <v>89940</v>
+        <v>89392</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11010,39 +10989,39 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3884</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Skarpan, Upl</t>
+          <t>Storvreta, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>649859.3531147883</v>
+        <v>650076.6066440826</v>
       </c>
       <c r="R88" t="n">
-        <v>6648977.102519212</v>
+        <v>6648711.587521225</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -11074,7 +11053,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11084,7 +11063,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11111,10 +11090,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>107841560</v>
+        <v>107848142</v>
       </c>
       <c r="B89" t="n">
-        <v>89392</v>
+        <v>89832</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11123,39 +11102,41 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Storvreta, Upl</t>
+          <t>Skarpan, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>650076.6066440826</v>
+        <v>649895.5850182869</v>
       </c>
       <c r="R89" t="n">
-        <v>6648711.587521225</v>
+        <v>6648975.56346914</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -11187,7 +11168,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11197,7 +11178,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11206,6 +11187,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -11224,10 +11206,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>107848142</v>
+        <v>107839659</v>
       </c>
       <c r="B90" t="n">
-        <v>89832</v>
+        <v>89392</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11236,31 +11218,29 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skarpan, Upl</t>
@@ -11302,7 +11282,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11312,7 +11292,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11321,7 +11301,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11340,10 +11319,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>107839659</v>
+        <v>107917446</v>
       </c>
       <c r="B91" t="n">
-        <v>89392</v>
+        <v>89940</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11352,42 +11331,44 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>3884</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Skarpan, Upl</t>
+          <t>Storvreta SV, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>649895.5850182869</v>
+        <v>649873.6361577424</v>
       </c>
       <c r="R91" t="n">
-        <v>6648975.56346914</v>
+        <v>6649058.423540089</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11411,22 +11392,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11435,28 +11416,29 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>107917446</v>
+        <v>108670120</v>
       </c>
       <c r="B92" t="n">
-        <v>89940</v>
+        <v>81972</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11465,25 +11447,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3884</v>
+        <v>1445</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11492,14 +11474,14 @@
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Storvreta SV, Upl</t>
+          <t>Himmelsvägen, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>649873.6361577424</v>
+        <v>649922.3442512245</v>
       </c>
       <c r="R92" t="n">
-        <v>6649058.423540089</v>
+        <v>6649058.895549387</v>
       </c>
       <c r="S92" t="n">
         <v>50</v>
@@ -11526,7 +11508,7 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-04-07</t>
+          <t>2023-04-30</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
@@ -11536,7 +11518,7 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-04-07</t>
+          <t>2023-04-30</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
@@ -11544,8 +11526,13 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ej återfunnen på tidigare känd lokal. Dålig status. Nästan alla granar i skogen har dött av granbarkborreangrepp. Båda delpopulationerna eftersökta.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
@@ -11557,22 +11544,26 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Moa Pettersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Moa Pettersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2023</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>108670120</v>
+        <v>111056277</v>
       </c>
       <c r="B93" t="n">
-        <v>81972</v>
+        <v>89405</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11581,44 +11572,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1445</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Himmelsvägen, Upl</t>
+          <t>Ekebylund, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>649922.3442512245</v>
+        <v>649920.2083246801</v>
       </c>
       <c r="R93" t="n">
-        <v>6649058.895549387</v>
+        <v>6648764.92085006</v>
       </c>
       <c r="S93" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11642,7 +11630,7 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2023-04-30</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
@@ -11652,7 +11640,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2023-04-30</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
@@ -11660,44 +11648,34 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ej återfunnen på tidigare känd lokal. Dålig status. Nästan alla granar i skogen har dött av granbarkborreangrepp. Båda delpopulationerna eftersökta.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Moa Pettersson</t>
+          <t>Karolina Bruce</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Moa Pettersson, Björn Larsson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2023</t>
-        </is>
-      </c>
+          <t>Erik Lagerin</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>111056277</v>
+        <v>111056282</v>
       </c>
       <c r="B94" t="n">
-        <v>89405</v>
+        <v>56414</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11710,34 +11688,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ekebylund, Upl</t>
+          <t>Vretalund, Upl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>649920.2083246801</v>
+        <v>649991.7194493939</v>
       </c>
       <c r="R94" t="n">
-        <v>6648764.92085006</v>
+        <v>6648636.920350144</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11806,7 +11784,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>111056282</v>
+        <v>111056258</v>
       </c>
       <c r="B95" t="n">
         <v>56414</v>
@@ -11840,16 +11818,24 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vretalund, Upl</t>
+          <t>Ekeby, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>649991.7194493939</v>
+        <v>649873.346980502</v>
       </c>
       <c r="R95" t="n">
-        <v>6648636.920350144</v>
+        <v>6649313.162568272</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11876,7 +11862,7 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
@@ -11886,12 +11872,17 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>gick ner Ö om obj</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11911,17 +11902,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Erik Lagerin</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>111056258</v>
+        <v>111056278</v>
       </c>
       <c r="B96" t="n">
-        <v>56414</v>
+        <v>89405</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11934,42 +11925,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ekeby, Upl</t>
+          <t>Ekebylund, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>649873.346980502</v>
+        <v>649983.1331478475</v>
       </c>
       <c r="R96" t="n">
-        <v>6649313.162568272</v>
+        <v>6648749.41955438</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11996,7 +11982,7 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
@@ -12006,7 +11992,7 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
@@ -12014,17 +12000,13 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>gick ner Ö om obj</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -12036,17 +12018,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>111056278</v>
+        <v>111789261</v>
       </c>
       <c r="B97" t="n">
-        <v>89405</v>
+        <v>88915</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12059,21 +12041,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>5734</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Druvfingersvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria botrytis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bourdot</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12082,17 +12064,17 @@
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ekebylund, Upl</t>
+          <t>Storvreta, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>649983.1331478475</v>
+        <v>650061</v>
       </c>
       <c r="R97" t="n">
-        <v>6648749.41955438</v>
+        <v>6648732</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12116,22 +12098,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12140,29 +12122,28 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Karolina Bruce</t>
+          <t>Henrik Lysell</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Henrik Lysell</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>111789261</v>
+        <v>111790355</v>
       </c>
       <c r="B98" t="n">
-        <v>88915</v>
+        <v>88909</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12171,31 +12152,29 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5734</v>
+        <v>720</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Storvreta, Upl</t>
@@ -12237,7 +12216,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12247,7 +12226,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Stort mycel (6 m diameter) intill ett kärr under en granlåga.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12274,10 +12258,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>111790355</v>
+        <v>111790914</v>
       </c>
       <c r="B99" t="n">
-        <v>88909</v>
+        <v>90662</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12286,42 +12270,42 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>720</v>
+        <v>4363</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Storvreta, Upl</t>
+          <t>Storvreta (Storvreta), Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>650061</v>
+        <v>650131</v>
       </c>
       <c r="R99" t="n">
-        <v>6648732</v>
+        <v>6648444</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12350,7 +12334,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12360,12 +12344,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Stort mycel (6 m diameter) intill ett kärr under en granlåga.</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12392,10 +12371,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>111790914</v>
+        <v>111789785</v>
       </c>
       <c r="B100" t="n">
-        <v>90662</v>
+        <v>90187</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12404,25 +12383,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4363</v>
+        <v>2014</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Scop.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12433,13 +12412,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>650131</v>
+        <v>649875</v>
       </c>
       <c r="R100" t="n">
-        <v>6648444</v>
+        <v>6648703</v>
       </c>
       <c r="S100" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12468,7 +12447,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12478,7 +12457,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>I starkt rötad asplåga. 2 fruktkroppar. Ca 70 meter ifrån skogsbrynet till en elledningsgata. Svårt att få exakt position pga mobiltäckning.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12505,10 +12489,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>111789785</v>
+        <v>111789319</v>
       </c>
       <c r="B101" t="n">
-        <v>90187</v>
+        <v>88915</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12521,21 +12505,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2014</v>
+        <v>5734</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Druvfingersvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Ramaria botrytis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
+          <t>(Pers.:Fr.) Bourdot</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12546,13 +12530,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>649875</v>
+        <v>650042</v>
       </c>
       <c r="R101" t="n">
-        <v>6648703</v>
+        <v>6648755</v>
       </c>
       <c r="S101" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12581,7 +12565,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12591,12 +12575,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>I starkt rötad asplåga. 2 fruktkroppar. Ca 70 meter ifrån skogsbrynet till en elledningsgata. Svårt att få exakt position pga mobiltäckning.</t>
+          <t>Mitt i en stigkorsning</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12607,6 +12591,11 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12623,10 +12612,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>111789319</v>
+        <v>111790550</v>
       </c>
       <c r="B102" t="n">
-        <v>88915</v>
+        <v>90655</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12635,25 +12624,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5734</v>
+        <v>150</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12664,13 +12653,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>650042</v>
+        <v>649935</v>
       </c>
       <c r="R102" t="n">
-        <v>6648755</v>
+        <v>6648620</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12699,7 +12688,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12709,12 +12698,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Mitt i en stigkorsning</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12725,11 +12709,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12746,10 +12725,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>111790550</v>
+        <v>111791986</v>
       </c>
       <c r="B103" t="n">
-        <v>90655</v>
+        <v>88982</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12758,42 +12737,42 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>150</v>
+        <v>937</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Storvreta (Storvreta), Upl</t>
+          <t>Storvreta, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>649935</v>
+        <v>650061</v>
       </c>
       <c r="R103" t="n">
-        <v>6648620</v>
+        <v>6648732</v>
       </c>
       <c r="S103" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12817,22 +12796,27 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Noterad ett år sent efter att ha problem med att rapportera! Två kraftigt rötade asplågor intill stig löpande N-&gt;S mellan Himmelsvägen och hästgården/huset efter skogen. Delar lågor med biskopsmössor.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12859,10 +12843,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>111791986</v>
+        <v>111789477</v>
       </c>
       <c r="B104" t="n">
-        <v>88982</v>
+        <v>88909</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12871,42 +12855,42 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>937</v>
+        <v>720</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Storvreta, Upl</t>
+          <t>Storvreta (Storvreta), Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>650061</v>
+        <v>649983</v>
       </c>
       <c r="R104" t="n">
-        <v>6648732</v>
+        <v>6648731</v>
       </c>
       <c r="S104" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12930,27 +12914,27 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Noterad ett år sent efter att ha problem med att rapportera! Två kraftigt rötade asplågor intill stig löpande N-&gt;S mellan Himmelsvägen och hästgården/huset efter skogen. Delar lågor med biskopsmössor.</t>
+          <t>Mellan stenblock ca 50 m bort ifrån föregående rapporterade mycel. Bland ett myller av granlågor.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12977,7 +12961,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>111789477</v>
+        <v>111789368</v>
       </c>
       <c r="B105" t="n">
         <v>88909</v>
@@ -13018,10 +13002,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>649983</v>
+        <v>650001</v>
       </c>
       <c r="R105" t="n">
-        <v>6648731</v>
+        <v>6648759</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13068,7 +13052,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Mellan stenblock ca 50 m bort ifrån föregående rapporterade mycel. Bland ett myller av granlågor.</t>
+          <t>I ett ca 5 meter långt stråk med många fruktkroppar.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13079,6 +13063,11 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -13095,10 +13084,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>111789368</v>
+        <v>111852345</v>
       </c>
       <c r="B106" t="n">
-        <v>88909</v>
+        <v>90844</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13107,25 +13096,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>720</v>
+        <v>5449</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13136,13 +13125,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>650001</v>
+        <v>650071</v>
       </c>
       <c r="R106" t="n">
-        <v>6648759</v>
+        <v>6648472</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13166,27 +13155,27 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>I ett ca 5 meter långt stråk med många fruktkroppar.</t>
+          <t>30 meter öster om annan samling. Bild saknas pga instabil hemsida!</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13197,11 +13186,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -13218,10 +13202,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>111852345</v>
+        <v>111961388</v>
       </c>
       <c r="B107" t="n">
-        <v>90844</v>
+        <v>90169</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13230,42 +13214,44 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5449</v>
+        <v>6031</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Storvreta (Storvreta), Upl</t>
+          <t>barrskog SV himmelsvägen, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>650071</v>
+        <v>650338</v>
       </c>
       <c r="R107" t="n">
-        <v>6648472</v>
+        <v>6648422</v>
       </c>
       <c r="S107" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13289,27 +13275,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>30 meter öster om annan samling. Bild saknas pga instabil hemsida!</t>
+          <t>vid basen av tall söder om stigen</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13318,28 +13294,29 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Henrik Lysell</t>
+          <t>Gry Benediktson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Henrik Lysell</t>
+          <t>Gry Benediktson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>111961388</v>
+        <v>111984708</v>
       </c>
       <c r="B108" t="n">
-        <v>90169</v>
+        <v>89057</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13348,44 +13325,42 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6031</v>
+        <v>720</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>barrskog SV himmelsvägen, Upl</t>
+          <t>Storvreta (Storvreta), Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>650338</v>
+        <v>650057</v>
       </c>
       <c r="R108" t="n">
-        <v>6648422</v>
+        <v>6648630</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13409,17 +13384,27 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>vid basen av tall söder om stigen</t>
+          <t>Under granar, precis intill kärret och en halvmeter från stig. Två samlingar.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13428,29 +13413,28 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Gry Benediktson</t>
+          <t>Henrik Lysell</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Gry Benediktson</t>
+          <t>Henrik Lysell</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>111984708</v>
+        <v>111984394</v>
       </c>
       <c r="B109" t="n">
-        <v>89057</v>
+        <v>90810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13459,25 +13443,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>720</v>
+        <v>4363</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13523,7 +13507,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13533,12 +13517,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Under granar, precis intill kärret och en halvmeter från stig. Två samlingar.</t>
+          <t>Nedanför granbacke i en stig (kärr ca 40 meter NV)</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13565,10 +13549,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>111984394</v>
+        <v>112063812</v>
       </c>
       <c r="B110" t="n">
-        <v>90810</v>
+        <v>90827</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13581,38 +13565,44 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4363</v>
+        <v>4366</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Storvreta (Storvreta), Upl</t>
+          <t>Barrskog V Himmelsvägen, Upl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>650057</v>
+        <v>650049</v>
       </c>
       <c r="R110" t="n">
-        <v>6648630</v>
+        <v>6648645</v>
       </c>
       <c r="S110" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13636,27 +13626,17 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Nedanför granbacke i en stig (kärr ca 40 meter NV)</t>
+          <t>Flera små, ganska torra, fruktkroppar</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13665,28 +13645,29 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Henrik Lysell</t>
+          <t>Gry Benediktson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Henrik Lysell</t>
+          <t>Gry Benediktson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>112063812</v>
+        <v>112139297</v>
       </c>
       <c r="B111" t="n">
-        <v>90827</v>
+        <v>89096</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13695,45 +13676,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4366</v>
+        <v>720</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Barrskog V Himmelsvägen, Upl</t>
+          <t>barrskog V himmelsvägen, Upl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>650049</v>
+        <v>650012</v>
       </c>
       <c r="R111" t="n">
-        <v>6648645</v>
+        <v>6648763</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13760,17 +13737,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Flera små, ganska torra, fruktkroppar</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13798,10 +13770,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>112139297</v>
+        <v>112139372</v>
       </c>
       <c r="B112" t="n">
-        <v>89096</v>
+        <v>90865</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13810,25 +13782,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>720</v>
+        <v>4366</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13841,10 +13813,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>650012</v>
+        <v>649886</v>
       </c>
       <c r="R112" t="n">
-        <v>6648763</v>
+        <v>6648971</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13877,6 +13849,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På/intill stigen</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13904,10 +13881,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>112139372</v>
+        <v>117810144</v>
       </c>
       <c r="B113" t="n">
-        <v>90865</v>
+        <v>57306</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13916,44 +13893,53 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>barrskog V himmelsvägen, Upl</t>
+          <t>barrskog SV himmelsvägen, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>649886</v>
+        <v>650088</v>
       </c>
       <c r="R113" t="n">
-        <v>6648971</v>
+        <v>6648774</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13977,17 +13963,17 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>På/intill stigen</t>
+          <t>Stannade till i 10min och lyssnade på återkommande rop/sång.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13996,7 +13982,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -14015,10 +14000,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>117810144</v>
+        <v>120120550</v>
       </c>
       <c r="B114" t="n">
-        <v>57306</v>
+        <v>91335</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14031,46 +14016,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>barrskog SV himmelsvägen, Upl</t>
+          <t>Ekebylund, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>650088</v>
+        <v>649753</v>
       </c>
       <c r="R114" t="n">
-        <v>6648774</v>
+        <v>6648844</v>
       </c>
       <c r="S114" t="n">
         <v>50</v>
@@ -14097,17 +14070,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Stannade till i 10min och lyssnade på återkommande rop/sång.</t>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14122,22 +14100,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Gry Benediktson</t>
+          <t>Erik Berg</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Gry Benediktson</t>
+          <t>Erik Berg</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120120550</v>
+        <v>120120595</v>
       </c>
       <c r="B115" t="n">
-        <v>91335</v>
+        <v>90141</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14150,21 +14128,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>366</v>
+        <v>937</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14209,7 +14187,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14219,7 +14197,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14246,10 +14224,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120120595</v>
+        <v>120121934</v>
       </c>
       <c r="B116" t="n">
-        <v>90141</v>
+        <v>91023</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14258,41 +14236,41 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>937</v>
+        <v>1209</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Ekebylund, Upl</t>
+          <t>Ekeby, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>649753</v>
+        <v>649910</v>
       </c>
       <c r="R116" t="n">
-        <v>6648844</v>
+        <v>6649024</v>
       </c>
       <c r="S116" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14321,7 +14299,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14331,7 +14309,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre barkborreträd</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14358,10 +14341,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120121934</v>
+        <v>120120686</v>
       </c>
       <c r="B117" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14370,38 +14353,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ekeby, Upl</t>
+          <t>Ekebylund, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>649910</v>
+        <v>649834</v>
       </c>
       <c r="R117" t="n">
-        <v>6649024</v>
+        <v>6648750</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -14433,7 +14416,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14443,12 +14426,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre barkborreträd</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14475,10 +14453,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120120686</v>
+        <v>120281713</v>
       </c>
       <c r="B118" t="n">
-        <v>90580</v>
+        <v>4772</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14487,41 +14465,46 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Ekebylund, Upl</t>
+          <t>Norrbo, Upl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>649834</v>
+        <v>650396</v>
       </c>
       <c r="R118" t="n">
-        <v>6648750</v>
+        <v>6648464</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14545,22 +14528,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14587,10 +14570,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120281713</v>
+        <v>123242068</v>
       </c>
       <c r="B119" t="n">
-        <v>4772</v>
+        <v>91435</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14599,46 +14582,44 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Norrbo, Upl</t>
+          <t>Storvreta, SV, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>650396</v>
+        <v>649926</v>
       </c>
       <c r="R119" t="n">
-        <v>6648464</v>
+        <v>6649068</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14662,22 +14643,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14686,142 +14657,37 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Erik Berg</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Erik Berg</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>123242068</v>
-      </c>
-      <c r="B120" t="n">
-        <v>91433</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>Storvreta, SV, Upl</t>
-        </is>
-      </c>
-      <c r="Q120" t="n">
-        <v>649926</v>
-      </c>
-      <c r="R120" t="n">
-        <v>6649068</v>
-      </c>
-      <c r="S120" t="n">
-        <v>10</v>
-      </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AD120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF120" t="inlineStr"/>
-      <c r="AG120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT120" t="inlineStr"/>
-      <c r="AW120" t="inlineStr">
-        <is>
-          <t>Björn Bråvander</t>
-        </is>
-      </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>Björn Bråvander</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
